--- a/Files/Alignment/metadata_fig_4.xlsx
+++ b/Files/Alignment/metadata_fig_4.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eugenianikonorova/Desktop/Work/Cornus_sericea_transcriptome_SDH/Files/Alignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2485CBD-2CA1-9C44-8454-4C32CBA7974E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917D6548-C923-BB4E-91C0-E12B766B6B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8140" yWindow="1440" windowWidth="27640" windowHeight="16940" xr2:uid="{103FD404-2B10-9747-BB60-C61F81904F5B}"/>
+    <workbookView xWindow="7220" yWindow="660" windowWidth="27640" windowHeight="16940" xr2:uid="{103FD404-2B10-9747-BB60-C61F81904F5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -55,15 +55,6 @@
     <t>EcDQD/SDH3</t>
   </si>
   <si>
-    <t>EgSDH1</t>
-  </si>
-  <si>
-    <t>EgSDH2</t>
-  </si>
-  <si>
-    <t>EgSDH3</t>
-  </si>
-  <si>
     <t>EgQDH1</t>
   </si>
   <si>
@@ -197,6 +188,15 @@
   </si>
   <si>
     <t>Cp_location</t>
+  </si>
+  <si>
+    <t>EgDQD/SDH1</t>
+  </si>
+  <si>
+    <t>EgDQD/SDH2</t>
+  </si>
+  <si>
+    <t>EgDQD/SDH3</t>
   </si>
 </sst>
 </file>
@@ -238,8 +238,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,16 +563,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -660,7 +661,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -674,7 +675,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -688,7 +689,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -702,7 +703,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -715,8 +716,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>8</v>
+      <c r="A12" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -730,7 +731,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -744,7 +745,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -758,7 +759,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -772,7 +773,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -786,7 +787,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -800,7 +801,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -814,7 +815,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -828,7 +829,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -842,7 +843,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -856,7 +857,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -870,7 +871,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -884,7 +885,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -898,7 +899,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -912,7 +913,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -926,7 +927,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -940,7 +941,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -954,7 +955,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -968,7 +969,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -982,7 +983,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -996,7 +997,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1010,7 +1011,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1024,7 +1025,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1038,7 +1039,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1052,7 +1053,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1066,7 +1067,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1080,7 +1081,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -1094,7 +1095,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -1108,7 +1109,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1122,7 +1123,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -1136,7 +1137,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -1145,12 +1146,12 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -1164,7 +1165,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -1178,7 +1179,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -1192,7 +1193,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1206,7 +1207,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1220,7 +1221,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1234,7 +1235,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1248,7 +1249,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1262,7 +1263,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B51">
         <v>0</v>

--- a/Files/Alignment/metadata_fig_4.xlsx
+++ b/Files/Alignment/metadata_fig_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eugenianikonorova/Desktop/Work/Cornus_sericea_transcriptome_SDH/Files/Alignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917D6548-C923-BB4E-91C0-E12B766B6B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93246B2A-88E1-6E4F-B8C4-0E2AFE2050FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7220" yWindow="660" windowWidth="27640" windowHeight="16940" xr2:uid="{103FD404-2B10-9747-BB60-C61F81904F5B}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="15120" windowHeight="17800" xr2:uid="{103FD404-2B10-9747-BB60-C61F81904F5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -238,9 +238,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,7 +599,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -614,7 +613,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -628,7 +627,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -656,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -716,7 +715,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>53</v>
       </c>
       <c r="B12">
@@ -796,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1146,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -1244,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">

--- a/Files/Alignment/metadata_fig_4.xlsx
+++ b/Files/Alignment/metadata_fig_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eugenianikonorova/Desktop/Work/Cornus_sericea_transcriptome_SDH/Files/Alignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93246B2A-88E1-6E4F-B8C4-0E2AFE2050FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4CADF6-0F4E-584A-B804-DF9DD7F65016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="15120" windowHeight="17800" xr2:uid="{103FD404-2B10-9747-BB60-C61F81904F5B}"/>
   </bookViews>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">

--- a/Files/Alignment/metadata_fig_4.xlsx
+++ b/Files/Alignment/metadata_fig_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eugenianikonorova/Desktop/Work/Cornus_sericea_transcriptome_SDH/Files/Alignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4CADF6-0F4E-584A-B804-DF9DD7F65016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F30904A-7793-094D-937E-347EEC207369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="15120" windowHeight="17800" xr2:uid="{103FD404-2B10-9747-BB60-C61F81904F5B}"/>
   </bookViews>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
